--- a/docs/d/03/inyear.xlsx
+++ b/docs/d/03/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 63 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 61 clubs short</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -918,8 +918,8 @@
       <c r="Y2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="9" t="n">
-        <v>0</v>
+      <c r="Z2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA2" s="10" t="n">
         <v>1</v>
@@ -4512,13 +4512,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4557,7 +4557,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>0</v>
@@ -6960,13 +6960,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>4</v>
       </c>
       <c r="W62" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X62" s="9" t="n">
         <v>1</v>
@@ -7047,7 +7047,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -7117,8 +7117,8 @@
       <c r="Y63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z63" s="9" t="n">
-        <v>0</v>
+      <c r="Z63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA63" s="10" t="n">
         <v>1</v>
@@ -15384,7 +15384,7 @@
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -15747,7 +15747,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>

--- a/docs/d/03/inyear.xlsx
+++ b/docs/d/03/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
         </is>
       </c>
     </row>
@@ -1945,7 +1945,11 @@
       <c r="AB12" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC12" s="4" t="inlineStr"/>
+      <c r="AC12" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -3266,7 +3270,11 @@
       <c r="AB25" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC25" s="4" t="inlineStr"/>
+      <c r="AC25" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -4375,7 +4383,11 @@
       <c r="AB36" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC36" s="4" t="inlineStr"/>
+      <c r="AC36" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -5292,7 +5304,11 @@
       <c r="AB45" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC45" s="4" t="inlineStr"/>
+      <c r="AC45" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -8451,7 +8467,11 @@
       <c r="AB76" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC76" s="4" t="inlineStr"/>
+      <c r="AC76" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -8552,7 +8572,11 @@
       <c r="AB77" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC77" s="4" t="inlineStr"/>
+      <c r="AC77" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -9481,7 +9505,11 @@
       <c r="AB86" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC86" s="4" t="inlineStr"/>
+      <c r="AC86" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -10907,7 +10935,11 @@
       <c r="AB100" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC100" s="4" t="inlineStr"/>
+      <c r="AC100" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -11008,7 +11040,11 @@
       <c r="AB101" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC101" s="4" t="inlineStr"/>
+      <c r="AC101" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -11416,7 +11452,11 @@
       <c r="AB105" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC105" s="4" t="inlineStr"/>
+      <c r="AC105" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -11929,7 +11969,11 @@
       <c r="AB110" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC110" s="4" t="inlineStr"/>
+      <c r="AC110" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -12753,7 +12797,11 @@
       <c r="AB118" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC118" s="4" t="inlineStr"/>
+      <c r="AC118" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -13060,7 +13108,11 @@
       <c r="AB121" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC121" s="4" t="inlineStr"/>
+      <c r="AC121" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
@@ -14785,7 +14837,11 @@
       <c r="AB138" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC138" s="4" t="inlineStr"/>
+      <c r="AC138" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">

--- a/docs/d/03/inyear.xlsx
+++ b/docs/d/03/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 20 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 20 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 61 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 55 clubs short</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="P16" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q16" s="9" t="n">
         <v>0</v>
@@ -2498,13 +2498,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W18" s="9" t="n">
         <v>0</v>
@@ -2989,7 +2989,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3059,8 +3059,8 @@
       <c r="Y23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z23" s="9" t="n">
-        <v>0</v>
+      <c r="Z23" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA23" s="10" t="n">
         <v>1</v>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="6" t="n">
         <v>10</v>
@@ -4786,8 +4786,8 @@
       <c r="Y40" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z40" s="9" t="n">
-        <v>0</v>
+      <c r="Z40" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA40" s="10" t="n">
         <v>1</v>
@@ -6760,7 +6760,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6830,8 +6830,8 @@
       <c r="Y60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z60" s="9" t="n">
-        <v>0</v>
+      <c r="Z60" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA60" s="10" t="n">
         <v>1</v>
@@ -9733,7 +9733,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9788,8 +9788,8 @@
       <c r="T89" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U89" s="9" t="n">
-        <v>0</v>
+      <c r="U89" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V89" s="9" t="n">
         <v>2</v>
@@ -9803,8 +9803,8 @@
       <c r="Y89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z89" s="9" t="n">
-        <v>0</v>
+      <c r="Z89" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA89" s="10" t="n">
         <v>1</v>
@@ -10650,7 +10650,7 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98" s="6" t="n">
         <v>10</v>
@@ -10720,8 +10720,8 @@
       <c r="Y98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z98" s="9" t="n">
-        <v>0</v>
+      <c r="Z98" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA98" s="10" t="n">
         <v>1</v>
@@ -10856,7 +10856,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10896,8 +10896,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P100" s="9" t="n">
-        <v>3</v>
+      <c r="P100" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Q100" s="10" t="n">
         <v>2</v>
@@ -12823,7 +12823,7 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12893,8 +12893,8 @@
       <c r="Y119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z119" s="9" t="n">
-        <v>0</v>
+      <c r="Z119" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA119" s="10" t="n">
         <v>1</v>
@@ -15572,7 +15572,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -15671,7 +15671,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -15803,7 +15803,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -15968,7 +15968,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -16034,7 +16034,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -16067,13 +16067,13 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -16199,7 +16199,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>

--- a/docs/d/03/inyear.xlsx
+++ b/docs/d/03/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 20 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 20 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 55 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 23 clubs short</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1322,8 +1322,8 @@
       <c r="Y6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" s="9" t="n">
-        <v>0</v>
+      <c r="Z6" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA6" s="10" t="n">
         <v>1</v>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1423,8 +1423,8 @@
       <c r="Y7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z7" s="9" t="n">
-        <v>0</v>
+      <c r="Z7" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA7" s="10" t="n">
         <v>1</v>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1726,8 +1726,8 @@
       <c r="Y10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z10" s="9" t="n">
-        <v>0</v>
+      <c r="Z10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA10" s="10" t="n">
         <v>1</v>
@@ -1916,7 +1916,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" s="10" t="n">
         <v>1</v>
@@ -2686,7 +2686,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2756,8 +2756,8 @@
       <c r="Y20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z20" s="9" t="n">
-        <v>0</v>
+      <c r="Z20" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA20" s="10" t="n">
         <v>1</v>
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -3160,8 +3160,8 @@
       <c r="Y24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z24" s="9" t="n">
-        <v>0</v>
+      <c r="Z24" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA24" s="10" t="n">
         <v>1</v>
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3465,8 +3465,8 @@
       <c r="Y27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z27" s="9" t="n">
-        <v>0</v>
+      <c r="Z27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA27" s="10" t="n">
         <v>1</v>
@@ -3669,8 +3669,8 @@
       <c r="Y29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z29" s="9" t="n">
-        <v>0</v>
+      <c r="Z29" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA29" s="9" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="6" t="n">
         <v>10</v>
@@ -3966,8 +3966,8 @@
       <c r="Y32" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z32" s="9" t="n">
-        <v>0</v>
+      <c r="Z32" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA32" s="10" t="n">
         <v>1</v>
@@ -4065,8 +4065,8 @@
       <c r="Y33" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z33" s="9" t="n">
-        <v>0</v>
+      <c r="Z33" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA33" s="9" t="n">
         <v>0</v>
@@ -5120,7 +5120,7 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F44" s="6" t="n">
         <v>10</v>
@@ -5175,8 +5175,8 @@
       <c r="T44" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U44" s="9" t="n">
-        <v>0</v>
+      <c r="U44" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V44" s="9" t="n">
         <v>2</v>
@@ -5532,7 +5532,7 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5602,8 +5602,8 @@
       <c r="Y48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z48" s="9" t="n">
-        <v>0</v>
+      <c r="Z48" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA48" s="10" t="n">
         <v>1</v>
@@ -5633,7 +5633,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5703,8 +5703,8 @@
       <c r="Y49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z49" s="9" t="n">
-        <v>0</v>
+      <c r="Z49" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA49" s="10" t="n">
         <v>1</v>
@@ -5734,7 +5734,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5804,8 +5804,8 @@
       <c r="Y50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z50" s="9" t="n">
-        <v>0</v>
+      <c r="Z50" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA50" s="10" t="n">
         <v>1</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5905,8 +5905,8 @@
       <c r="Y51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z51" s="9" t="n">
-        <v>0</v>
+      <c r="Z51" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA51" s="10" t="n">
         <v>1</v>
@@ -5936,7 +5936,7 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -5988,8 +5988,8 @@
       <c r="S52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T52" s="9" t="n">
-        <v>0</v>
+      <c r="T52" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U52" s="9" t="n">
         <v>0</v>
@@ -6243,7 +6243,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6313,8 +6313,8 @@
       <c r="Y55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z55" s="9" t="n">
-        <v>0</v>
+      <c r="Z55" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA55" s="10" t="n">
         <v>1</v>
@@ -6348,7 +6348,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6418,8 +6418,8 @@
       <c r="Y56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z56" s="9" t="n">
-        <v>0</v>
+      <c r="Z56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA56" s="10" t="n">
         <v>1</v>
@@ -7234,8 +7234,8 @@
       <c r="Y64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z64" s="9" t="n">
-        <v>0</v>
+      <c r="Z64" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA64" s="9" t="n">
         <v>0</v>
@@ -7572,7 +7572,7 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7642,8 +7642,8 @@
       <c r="Y68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z68" s="9" t="n">
-        <v>0</v>
+      <c r="Z68" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA68" s="10" t="n">
         <v>1</v>
@@ -7673,7 +7673,7 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7743,8 +7743,8 @@
       <c r="Y69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z69" s="9" t="n">
-        <v>0</v>
+      <c r="Z69" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA69" s="10" t="n">
         <v>1</v>
@@ -8077,7 +8077,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8147,8 +8147,8 @@
       <c r="Y73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z73" s="9" t="n">
-        <v>0</v>
+      <c r="Z73" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA73" s="10" t="n">
         <v>1</v>
@@ -8534,7 +8534,7 @@
         </is>
       </c>
       <c r="P77" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q77" s="9" t="n">
         <v>0</v>
@@ -9189,8 +9189,8 @@
       <c r="Y83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z83" s="9" t="n">
-        <v>0</v>
+      <c r="Z83" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA83" s="9" t="n">
         <v>0</v>
@@ -10246,7 +10246,7 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F94" s="6" t="n">
         <v>10</v>
@@ -10316,8 +10316,8 @@
       <c r="Y94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z94" s="9" t="n">
-        <v>0</v>
+      <c r="Z94" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA94" s="10" t="n">
         <v>1</v>
@@ -10518,8 +10518,8 @@
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="9" t="n">
-        <v>0</v>
+      <c r="Z96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA96" s="9" t="n">
         <v>0</v>
@@ -10549,7 +10549,7 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10619,8 +10619,8 @@
       <c r="Y97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" s="9" t="n">
-        <v>0</v>
+      <c r="Z97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA97" s="10" t="n">
         <v>1</v>
@@ -11066,7 +11066,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -11136,8 +11136,8 @@
       <c r="Y102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z102" s="9" t="n">
-        <v>0</v>
+      <c r="Z102" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA102" s="10" t="n">
         <v>1</v>
@@ -11272,7 +11272,7 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -11342,8 +11342,8 @@
       <c r="Y104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z104" s="9" t="n">
-        <v>0</v>
+      <c r="Z104" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA104" s="10" t="n">
         <v>1</v>
@@ -12065,8 +12065,8 @@
       <c r="Y111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z111" s="9" t="n">
-        <v>0</v>
+      <c r="Z111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA111" s="9" t="n">
         <v>0</v>
@@ -12732,13 +12732,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>4</v>
       </c>
       <c r="W118" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X118" s="10" t="n">
         <v>6</v>
@@ -13029,7 +13029,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -13081,8 +13081,8 @@
       <c r="S121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T121" s="9" t="n">
-        <v>0</v>
+      <c r="T121" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U121" s="9" t="n">
         <v>0</v>
@@ -13482,7 +13482,7 @@
         </is>
       </c>
       <c r="P125" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q125" s="9" t="n">
         <v>1</v>
@@ -13542,7 +13542,7 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -13612,8 +13612,8 @@
       <c r="Y126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z126" s="9" t="n">
-        <v>0</v>
+      <c r="Z126" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA126" s="10" t="n">
         <v>1</v>
@@ -13744,7 +13744,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13814,8 +13814,8 @@
       <c r="Y128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z128" s="9" t="n">
-        <v>0</v>
+      <c r="Z128" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA128" s="10" t="n">
         <v>1</v>
@@ -14117,8 +14117,8 @@
       <c r="Y131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z131" s="9" t="n">
-        <v>0</v>
+      <c r="Z131" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA131" s="9" t="n">
         <v>0</v>
@@ -14152,7 +14152,7 @@
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -14222,8 +14222,8 @@
       <c r="Y132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z132" s="9" t="n">
-        <v>0</v>
+      <c r="Z132" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA132" s="10" t="n">
         <v>1</v>
@@ -14657,7 +14657,7 @@
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -14727,8 +14727,8 @@
       <c r="Y137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z137" s="9" t="n">
-        <v>0</v>
+      <c r="Z137" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA137" s="10" t="n">
         <v>1</v>
@@ -14772,13 +14772,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>0</v>
       </c>
       <c r="V138" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W138" s="9" t="n">
         <v>0</v>
@@ -15106,7 +15106,7 @@
         </is>
       </c>
       <c r="P141" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q141" s="9" t="n">
         <v>0</v>
@@ -15166,7 +15166,7 @@
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F142" s="6" t="n">
         <v>10</v>
@@ -15236,8 +15236,8 @@
       <c r="Y142" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z142" s="9" t="n">
-        <v>0</v>
+      <c r="Z142" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA142" s="10" t="n">
         <v>1</v>
@@ -15473,7 +15473,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -15539,7 +15539,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -15572,7 +15572,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -15605,7 +15605,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -15671,7 +15671,7 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -15704,7 +15704,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -15737,7 +15737,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -15770,7 +15770,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -15836,7 +15836,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -15869,7 +15869,7 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -16034,7 +16034,7 @@
         <v>5</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -16067,7 +16067,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -16100,7 +16100,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -16199,7 +16199,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -16232,7 +16232,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -16265,7 +16265,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -16298,7 +16298,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
         <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>

--- a/docs/d/03/inyear.xlsx
+++ b/docs/d/03/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 20 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 20 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 23 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 23 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -963,13 +963,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1064,13 +1064,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1165,17 +1165,17 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-23</v>
+      </c>
+      <c r="L5" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M5" s="8" t="n">
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W6" s="9" t="n">
         <v>0</v>
@@ -1412,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="V7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" s="9" t="n">
         <v>0</v>
@@ -1468,13 +1468,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1670,13 +1670,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -1699,8 +1699,8 @@
       <c r="P10" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" s="9" t="n">
-        <v>1</v>
+      <c r="Q10" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R10" s="9" t="n">
         <v>0</v>
@@ -1714,8 +1714,8 @@
       <c r="U10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V10" s="9" t="n">
-        <v>2</v>
+      <c r="V10" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>0</v>
@@ -1775,13 +1775,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>2</v>
       </c>
       <c r="Q11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" s="9" t="n">
         <v>0</v>
@@ -1820,7 +1820,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1880,13 +1880,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3</v>
+        <v>-11</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
@@ -1924,8 +1924,8 @@
       <c r="U12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V12" s="9" t="n">
-        <v>3</v>
+      <c r="V12" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W12" s="9" t="n">
         <v>0</v>
@@ -1985,13 +1985,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2086,17 +2086,17 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M14" s="8" t="n">
@@ -2113,7 +2113,7 @@
         </is>
       </c>
       <c r="P14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" s="9" t="n">
         <v>0</v>
@@ -2191,13 +2191,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2292,13 +2292,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2393,17 +2393,17 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M17" s="8" t="n">
@@ -2437,11 +2437,11 @@
       <c r="U17" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V17" s="9" t="n">
-        <v>2</v>
+      <c r="V17" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X17" s="10" t="n">
         <v>5</v>
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2542,8 +2542,8 @@
       <c r="U18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V18" s="9" t="n">
-        <v>3</v>
+      <c r="V18" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W18" s="9" t="n">
         <v>0</v>
@@ -2599,13 +2599,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2700,13 +2700,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>10</v>
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="Q21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T21" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U21" s="9" t="n">
         <v>0</v>
@@ -2902,13 +2902,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
@@ -3003,13 +3003,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -3104,13 +3104,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="V24" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W24" s="9" t="n">
         <v>0</v>
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3205,13 +3205,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3</v>
+        <v>-9</v>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
@@ -3249,11 +3249,11 @@
       <c r="U25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V25" s="9" t="n">
-        <v>3</v>
+      <c r="V25" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W25" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X25" s="10" t="n">
         <v>7</v>
@@ -3310,13 +3310,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="V26" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W26" s="9" t="n">
         <v>0</v>
@@ -3409,17 +3409,17 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M27" s="8" t="n">
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3514,13 +3514,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3558,8 +3558,8 @@
       <c r="U28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V28" s="9" t="n">
-        <v>3</v>
+      <c r="V28" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W28" s="9" t="n">
         <v>0</v>
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3613,13 +3613,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
@@ -3657,11 +3657,11 @@
       <c r="U29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V29" s="9" t="n">
-        <v>0</v>
+      <c r="V29" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W29" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X29" s="10" t="n">
         <v>6</v>
@@ -3712,13 +3712,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>35</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
@@ -3811,13 +3811,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3910,13 +3910,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -4009,13 +4009,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -4108,17 +4108,17 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L34" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M34" s="8" t="n">
@@ -4213,17 +4213,17 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L35" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M35" s="8" t="n">
@@ -4240,7 +4240,7 @@
         </is>
       </c>
       <c r="P35" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q35" s="9" t="n">
         <v>0</v>
@@ -4318,13 +4318,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>7</v>
+        <v>-6</v>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
@@ -4524,13 +4524,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4569,7 +4569,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>0</v>
@@ -4730,13 +4730,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         <v>0</v>
       </c>
       <c r="V40" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W40" s="9" t="n">
         <v>0</v>
@@ -4831,13 +4831,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="V41" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W41" s="9" t="n">
         <v>0</v>
@@ -5134,17 +5134,17 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L44" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M44" s="8" t="n">
@@ -5179,7 +5179,7 @@
         <v>1</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5239,13 +5239,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
@@ -5344,13 +5344,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -5445,13 +5445,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>0</v>
@@ -5633,7 +5633,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5647,13 +5647,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
@@ -5691,11 +5691,11 @@
       <c r="U49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V49" s="9" t="n">
-        <v>0</v>
+      <c r="V49" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W49" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X49" s="9" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5748,13 +5748,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5792,8 +5792,8 @@
       <c r="U50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V50" s="9" t="n">
-        <v>2</v>
+      <c r="V50" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W50" s="9" t="n">
         <v>0</v>
@@ -5849,13 +5849,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>0</v>
       </c>
       <c r="V51" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W51" s="9" t="n">
         <v>0</v>
@@ -5950,13 +5950,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
@@ -6055,13 +6055,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -6142,7 +6142,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -6156,13 +6156,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -6185,8 +6185,8 @@
       <c r="P54" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q54" s="9" t="n">
-        <v>1</v>
+      <c r="Q54" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R54" s="9" t="n">
         <v>0</v>
@@ -6257,13 +6257,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6362,13 +6362,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -6463,13 +6463,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6564,13 +6564,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>0</v>
       </c>
       <c r="V58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W58" s="9" t="n">
         <v>0</v>
@@ -6669,13 +6669,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -6696,7 +6696,7 @@
         </is>
       </c>
       <c r="P59" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q59" s="9" t="n">
         <v>0</v>
@@ -6774,13 +6774,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -6875,13 +6875,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -6976,13 +6976,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
@@ -7178,17 +7178,17 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L64" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L64" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M64" s="8" t="n">
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7384,17 +7384,17 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L66" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M66" s="8" t="n">
@@ -7429,7 +7429,7 @@
         <v>0</v>
       </c>
       <c r="V66" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
@@ -7586,13 +7586,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7687,13 +7687,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>0</v>
       </c>
       <c r="V69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -7788,13 +7788,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>4</v>
+        <v>-10</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>4</v>
       </c>
       <c r="W71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X71" s="9" t="n">
         <v>0</v>
@@ -7990,17 +7990,17 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L72" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-23</v>
+      </c>
+      <c r="L72" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M72" s="8" t="n">
@@ -8091,17 +8091,17 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L73" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M73" s="8" t="n">
@@ -8196,13 +8196,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         <v>0</v>
       </c>
       <c r="S74" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T74" s="9" t="n">
         <v>0</v>
@@ -8297,13 +8297,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8402,13 +8402,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
@@ -8428,8 +8428,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P76" s="9" t="n">
-        <v>3</v>
+      <c r="P76" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q76" s="9" t="n">
         <v>0</v>
@@ -8507,13 +8507,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
@@ -8612,17 +8612,17 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L78" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M78" s="8" t="n">
@@ -8927,13 +8927,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -9028,17 +9028,17 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L82" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L82" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M82" s="8" t="n">
@@ -9133,13 +9133,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -9234,17 +9234,17 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L84" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L84" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M84" s="8" t="n">
@@ -9279,7 +9279,7 @@
         <v>0</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
@@ -9335,13 +9335,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9440,13 +9440,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
@@ -9484,8 +9484,8 @@
       <c r="U86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V86" s="9" t="n">
-        <v>2</v>
+      <c r="V86" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W86" s="9" t="n">
         <v>0</v>
@@ -9545,13 +9545,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
@@ -9646,13 +9646,13 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9747,13 +9747,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9791,8 +9791,8 @@
       <c r="U89" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V89" s="9" t="n">
-        <v>2</v>
+      <c r="V89" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -9834,7 +9834,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9848,13 +9848,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -9892,11 +9892,11 @@
       <c r="U90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V90" s="9" t="n">
-        <v>3</v>
+      <c r="V90" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W90" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X90" s="10" t="n">
         <v>6</v>
@@ -9953,13 +9953,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -10054,13 +10054,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>0</v>
       </c>
       <c r="V92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W92" s="9" t="n">
         <v>0</v>
@@ -10155,17 +10155,17 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L93" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L93" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M93" s="8" t="n">
@@ -10260,13 +10260,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -10305,7 +10305,7 @@
         <v>0</v>
       </c>
       <c r="V94" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W94" s="9" t="n">
         <v>0</v>
@@ -10361,13 +10361,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -10462,17 +10462,17 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L96" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M96" s="8" t="n">
@@ -10507,7 +10507,7 @@
         <v>0</v>
       </c>
       <c r="V96" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
@@ -10563,17 +10563,17 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L97" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M97" s="8" t="n">
@@ -10664,13 +10664,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>0</v>
       </c>
       <c r="V98" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W98" s="9" t="n">
         <v>0</v>
@@ -10765,17 +10765,17 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L99" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M99" s="8" t="n">
@@ -10792,7 +10792,7 @@
         </is>
       </c>
       <c r="P99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q99" s="9" t="n">
         <v>1</v>
@@ -10870,13 +10870,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>5</v>
+        <v>-4</v>
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>4</v>
       </c>
       <c r="W100" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X100" s="10" t="n">
         <v>5</v>
@@ -10975,13 +10975,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
@@ -11080,13 +11080,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -11181,13 +11181,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -11286,13 +11286,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>0</v>
       </c>
       <c r="V104" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
@@ -11387,13 +11387,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>51</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
@@ -11432,7 +11432,7 @@
         <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
@@ -11492,13 +11492,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11593,13 +11593,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11694,13 +11694,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11735,8 +11735,8 @@
       <c r="T108" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U108" s="9" t="n">
-        <v>0</v>
+      <c r="U108" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V108" s="9" t="n">
         <v>0</v>
@@ -11799,13 +11799,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -11844,7 +11844,7 @@
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
@@ -11904,13 +11904,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -11995,7 +11995,7 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -12009,17 +12009,17 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L111" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>9</v>
+      </c>
+      <c r="L111" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M111" s="8" t="n">
@@ -12053,11 +12053,11 @@
       <c r="U111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V111" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W111" s="9" t="n">
-        <v>0</v>
+      <c r="V111" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W111" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X111" s="9" t="n">
         <v>0</v>
@@ -12110,13 +12110,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
@@ -12215,17 +12215,17 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L113" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L113" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M113" s="8" t="n">
@@ -12320,13 +12320,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -12421,13 +12421,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -12522,13 +12522,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
@@ -12627,13 +12627,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
@@ -12732,13 +12732,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
@@ -12837,13 +12837,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -12942,13 +12942,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -13043,13 +13043,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
@@ -13148,13 +13148,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>0</v>
       </c>
       <c r="V122" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
@@ -13249,13 +13249,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -13350,13 +13350,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
@@ -13379,8 +13379,8 @@
       <c r="P124" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q124" s="9" t="n">
-        <v>1</v>
+      <c r="Q124" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R124" s="9" t="n">
         <v>0</v>
@@ -13455,13 +13455,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
         <v>1</v>
       </c>
       <c r="V125" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W125" s="9" t="n">
         <v>0</v>
@@ -13657,13 +13657,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -13758,13 +13758,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
@@ -13859,13 +13859,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
@@ -13960,13 +13960,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
@@ -14061,13 +14061,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -14152,7 +14152,7 @@
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -14166,13 +14166,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
@@ -14210,11 +14210,11 @@
       <c r="U132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V132" s="9" t="n">
-        <v>1</v>
+      <c r="V132" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W132" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X132" s="9" t="n">
         <v>2</v>
@@ -14267,17 +14267,17 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L133" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-22</v>
+      </c>
+      <c r="L133" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M133" s="8" t="n">
@@ -14368,13 +14368,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>0</v>
       </c>
       <c r="V134" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W134" s="9" t="n">
         <v>0</v>
@@ -14455,7 +14455,7 @@
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -14469,13 +14469,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
@@ -14513,8 +14513,8 @@
       <c r="U135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V135" s="9" t="n">
-        <v>3</v>
+      <c r="V135" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W135" s="9" t="n">
         <v>0</v>
@@ -14556,7 +14556,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -14570,13 +14570,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -14614,11 +14614,11 @@
       <c r="U136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V136" s="9" t="n">
-        <v>1</v>
+      <c r="V136" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W136" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X136" s="10" t="n">
         <v>5</v>
@@ -14671,13 +14671,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -14772,13 +14772,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
@@ -14877,17 +14877,17 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L139" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L139" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M139" s="8" t="n">
@@ -14925,7 +14925,7 @@
         <v>4</v>
       </c>
       <c r="W139" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X139" s="10" t="n">
         <v>7</v>
@@ -15079,17 +15079,17 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L141" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L141" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M141" s="8" t="n">
@@ -15180,13 +15180,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>0</v>
       </c>
       <c r="V142" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W142" s="9" t="n">
         <v>0</v>
@@ -15281,17 +15281,17 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L143" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-18</v>
+      </c>
+      <c r="L143" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M143" s="8" t="n">
@@ -15326,7 +15326,7 @@
         <v>0</v>
       </c>
       <c r="V143" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W143" s="9" t="n">
         <v>0</v>
@@ -15455,7 +15455,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -15473,7 +15473,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -15506,7 +15506,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -15521,7 +15521,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -15539,7 +15539,7 @@
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -15554,7 +15554,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -15572,7 +15572,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -15587,7 +15587,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -15605,7 +15605,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -15653,7 +15653,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -15686,7 +15686,7 @@
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -15704,7 +15704,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -15737,7 +15737,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -15818,7 +15818,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -15851,7 +15851,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -15884,7 +15884,7 @@
         <v>1</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -15902,7 +15902,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -15917,7 +15917,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -15950,7 +15950,7 @@
         <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -15968,7 +15968,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -15983,7 +15983,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -16001,7 +16001,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -16016,7 +16016,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -16082,7 +16082,7 @@
         <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -16100,7 +16100,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -16133,7 +16133,7 @@
         <v>5</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
@@ -16232,7 +16232,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -16298,7 +16298,7 @@
         <v>6</v>
       </c>
       <c r="D28" t="n">
-        <v>0.83</v>
+        <v>1.33</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -16313,7 +16313,7 @@
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -16346,7 +16346,7 @@
         <v>2</v>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/03/inyear.xlsx
+++ b/docs/d/03/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/03/inyear.xlsx
+++ b/docs/d/03/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/03/inyear.xlsx
+++ b/docs/d/03/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/03/inyear.xlsx
+++ b/docs/d/03/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/03/inyear.xlsx
+++ b/docs/d/03/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 20 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 20 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 23 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 23 clubs short</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1506,8 +1506,8 @@
       <c r="S8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T8" s="9" t="n">
-        <v>0</v>
+      <c r="T8" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U8" s="9" t="n">
         <v>0</v>
@@ -1775,13 +1775,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -2599,13 +2599,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         </is>
       </c>
       <c r="P19" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="9" t="n">
         <v>0</v>
@@ -3205,13 +3205,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
@@ -4009,13 +4009,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" s="6" t="n">
         <v>10</v>
@@ -4239,8 +4239,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P35" s="9" t="n">
-        <v>3</v>
+      <c r="P35" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q35" s="9" t="n">
         <v>0</v>
@@ -4318,13 +4318,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         </is>
       </c>
       <c r="P38" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q38" s="9" t="n">
         <v>0</v>
@@ -5647,13 +5647,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
@@ -5695,7 +5695,7 @@
         <v>4</v>
       </c>
       <c r="W49" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X49" s="9" t="n">
         <v>0</v>
@@ -5748,13 +5748,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>1</v>
       </c>
       <c r="U53" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V53" s="9" t="n">
         <v>0</v>
@@ -6348,7 +6348,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6403,8 +6403,8 @@
       <c r="T56" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U56" s="9" t="n">
-        <v>0</v>
+      <c r="U56" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V56" s="9" t="n">
         <v>1</v>
@@ -8091,13 +8091,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>0</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
@@ -8196,13 +8196,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -8612,13 +8612,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -9028,13 +9028,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         <v>0</v>
       </c>
       <c r="V82" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
@@ -9133,13 +9133,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         </is>
       </c>
       <c r="P95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q95" s="10" t="n">
         <v>2</v>
@@ -10397,7 +10397,7 @@
         <v>1</v>
       </c>
       <c r="S95" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T95" s="10" t="n">
         <v>1</v>
@@ -10765,13 +10765,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -11286,13 +11286,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -11331,7 +11331,7 @@
         <v>0</v>
       </c>
       <c r="V104" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W104" s="9" t="n">
         <v>0</v>
@@ -11904,13 +11904,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         <v>4</v>
       </c>
       <c r="W110" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X110" s="10" t="n">
         <v>7</v>
@@ -13043,13 +13043,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
@@ -13148,13 +13148,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -13657,13 +13657,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -13702,7 +13702,7 @@
         <v>0</v>
       </c>
       <c r="V127" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W127" s="9" t="n">
         <v>0</v>
@@ -13758,13 +13758,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>0</v>
       </c>
       <c r="V128" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
@@ -14520,7 +14520,7 @@
         <v>0</v>
       </c>
       <c r="X135" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y135" s="9" t="n">
         <v>0</v>
@@ -14570,13 +14570,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -14618,7 +14618,7 @@
         <v>4</v>
       </c>
       <c r="W136" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X136" s="10" t="n">
         <v>5</v>
@@ -15180,13 +15180,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>10</v>
@@ -15317,10 +15317,10 @@
         <v>0</v>
       </c>
       <c r="S143" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T143" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T143" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U143" s="9" t="n">
         <v>0</v>
@@ -15473,7 +15473,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -15638,7 +15638,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -15770,7 +15770,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -16331,7 +16331,7 @@
         <v>6</v>
       </c>
       <c r="D29" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>

--- a/docs/d/03/inyear.xlsx
+++ b/docs/d/03/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:49 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 20 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 20 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 23 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 23 clubs short</t>
         </is>
       </c>
     </row>
@@ -2086,13 +2086,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
@@ -3205,13 +3205,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>4</v>
       </c>
       <c r="W25" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X25" s="10" t="n">
         <v>7</v>
@@ -3514,13 +3514,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         </is>
       </c>
       <c r="P28" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q28" s="9" t="n">
         <v>0</v>
@@ -4318,13 +4318,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
@@ -4629,13 +4629,13 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
         <v>0</v>
       </c>
       <c r="V39" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W39" s="9" t="n">
         <v>0</v>
@@ -5748,13 +5748,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>4</v>
       </c>
       <c r="W50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X50" s="9" t="n">
         <v>0</v>
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>-10</v>
+        <v>-7</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>4</v>
       </c>
       <c r="W71" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X71" s="9" t="n">
         <v>0</v>
@@ -8388,7 +8388,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8402,13 +8402,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
@@ -8446,8 +8446,8 @@
       <c r="U76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V76" s="9" t="n">
-        <v>3</v>
+      <c r="V76" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -9055,7 +9055,7 @@
         </is>
       </c>
       <c r="P82" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q82" s="9" t="n">
         <v>1</v>
@@ -9133,13 +9133,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9878,7 +9878,7 @@
         <v>0</v>
       </c>
       <c r="Q90" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R90" s="9" t="n">
         <v>0</v>
@@ -9889,8 +9889,8 @@
       <c r="T90" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U90" s="9" t="n">
-        <v>0</v>
+      <c r="U90" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V90" s="10" t="n">
         <v>4</v>
@@ -10856,7 +10856,7 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10902,8 +10902,8 @@
       <c r="Q100" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R100" s="9" t="n">
-        <v>1</v>
+      <c r="R100" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S100" s="10" t="n">
         <v>2</v>
@@ -11181,13 +11181,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -11492,13 +11492,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11904,13 +11904,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>42</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         <v>4</v>
       </c>
       <c r="W110" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X110" s="10" t="n">
         <v>7</v>
@@ -12768,7 +12768,7 @@
         <v>0</v>
       </c>
       <c r="S118" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T118" s="10" t="n">
         <v>1</v>
@@ -13029,7 +13029,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -13043,13 +13043,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
@@ -13087,8 +13087,8 @@
       <c r="U121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V121" s="9" t="n">
-        <v>2</v>
+      <c r="V121" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W121" s="9" t="n">
         <v>0</v>
@@ -13455,13 +13455,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>1</v>
       </c>
       <c r="U125" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V125" s="9" t="n">
         <v>2</v>
@@ -14877,13 +14877,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J139" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
@@ -15902,7 +15902,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16001,7 +16001,7 @@
         <v>4</v>
       </c>
       <c r="D19" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -16067,7 +16067,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -16199,7 +16199,7 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
